--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5141,10 +5141,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121259711</v>
+        <v>121259712</v>
       </c>
       <c r="B40" t="n">
-        <v>90652</v>
+        <v>91137</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5153,25 +5153,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5182,14 +5182,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>551324</v>
+        <v>551637</v>
       </c>
       <c r="R40" t="n">
-        <v>6636145</v>
+        <v>6636229</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5224,11 +5224,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Barklös granlåga</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5237,23 +5232,13 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AN40" t="n">
         <v>1</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5271,10 +5256,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259712</v>
+        <v>121259765</v>
       </c>
       <c r="B41" t="n">
-        <v>91127</v>
+        <v>98081</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5287,39 +5272,53 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551637</v>
+        <v>551423</v>
       </c>
       <c r="R41" t="n">
-        <v>6636229</v>
+        <v>6636218</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5354,6 +5353,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5362,14 +5366,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5386,10 +5382,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259765</v>
+        <v>121259711</v>
       </c>
       <c r="B42" t="n">
-        <v>98071</v>
+        <v>90662</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5398,57 +5394,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551423</v>
+        <v>551324</v>
       </c>
       <c r="R42" t="n">
-        <v>6636218</v>
+        <v>6636145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5485,7 +5467,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
+          <t>Barklös granlåga</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5496,6 +5478,24 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5512,10 +5512,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259709</v>
+        <v>121259767</v>
       </c>
       <c r="B43" t="n">
-        <v>91127</v>
+        <v>98081</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5528,39 +5528,53 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551258</v>
+        <v>551637</v>
       </c>
       <c r="R43" t="n">
-        <v>6636221</v>
+        <v>6636228</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5603,24 +5617,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5640,7 +5636,7 @@
         <v>121259797</v>
       </c>
       <c r="B44" t="n">
-        <v>43704</v>
+        <v>43707</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5783,10 +5779,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259767</v>
+        <v>121259766</v>
       </c>
       <c r="B45" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5818,7 +5814,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5845,7 +5841,7 @@
         <v>551637</v>
       </c>
       <c r="R45" t="n">
-        <v>6636228</v>
+        <v>6636229</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5904,10 +5900,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121259764</v>
+        <v>121259709</v>
       </c>
       <c r="B46" t="n">
-        <v>98071</v>
+        <v>91137</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5920,53 +5916,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551417</v>
+        <v>551258</v>
       </c>
       <c r="R46" t="n">
-        <v>6636227</v>
+        <v>6636221</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6009,6 +5991,24 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121259766</v>
+        <v>121259710</v>
       </c>
       <c r="B47" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6037,57 +6037,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551637</v>
+        <v>551258</v>
       </c>
       <c r="R47" t="n">
-        <v>6636229</v>
+        <v>6636221</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6130,6 +6116,24 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6146,10 +6150,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121259710</v>
+        <v>121259764</v>
       </c>
       <c r="B48" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6158,43 +6162,57 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551258</v>
+        <v>551417</v>
       </c>
       <c r="R48" t="n">
-        <v>6636221</v>
+        <v>6636227</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6237,24 +6255,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5256,10 +5256,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259765</v>
+        <v>121259711</v>
       </c>
       <c r="B41" t="n">
-        <v>98081</v>
+        <v>90662</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5268,57 +5268,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551423</v>
+        <v>551324</v>
       </c>
       <c r="R41" t="n">
-        <v>6636218</v>
+        <v>6636145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5355,7 +5341,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
+          <t>Barklös granlåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5366,6 +5352,24 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5382,10 +5386,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259711</v>
+        <v>121259765</v>
       </c>
       <c r="B42" t="n">
-        <v>90662</v>
+        <v>98081</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5394,43 +5398,57 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551324</v>
+        <v>551423</v>
       </c>
       <c r="R42" t="n">
-        <v>6636145</v>
+        <v>6636218</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5467,7 +5485,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Barklös granlåga</t>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5478,24 +5496,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5256,10 +5256,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259711</v>
+        <v>121259797</v>
       </c>
       <c r="B41" t="n">
-        <v>90662</v>
+        <v>43707</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5272,27 +5272,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>101735</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>kokong</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5301,10 +5320,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551324</v>
+        <v>551271</v>
       </c>
       <c r="R41" t="n">
-        <v>6636145</v>
+        <v>6636238</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5341,7 +5360,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Barklös granlåga</t>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5355,20 +5374,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN41" t="n">
-        <v>1</v>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5386,10 +5402,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259765</v>
+        <v>121259709</v>
       </c>
       <c r="B42" t="n">
-        <v>98081</v>
+        <v>91137</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5402,53 +5418,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551423</v>
+        <v>551258</v>
       </c>
       <c r="R42" t="n">
-        <v>6636218</v>
+        <v>6636221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5483,11 +5485,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5496,6 +5493,24 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5512,7 +5527,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259767</v>
+        <v>121259765</v>
       </c>
       <c r="B43" t="n">
         <v>98081</v>
@@ -5552,12 +5567,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5567,14 +5582,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551637</v>
+        <v>551423</v>
       </c>
       <c r="R43" t="n">
-        <v>6636228</v>
+        <v>6636218</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5607,6 +5622,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5633,10 +5653,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259797</v>
+        <v>121259766</v>
       </c>
       <c r="B44" t="n">
-        <v>43707</v>
+        <v>98081</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5645,25 +5665,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5673,17 +5693,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>kokong</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5693,14 +5708,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551271</v>
+        <v>551637</v>
       </c>
       <c r="R44" t="n">
-        <v>6636238</v>
+        <v>6636229</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5735,11 +5750,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5748,21 +5758,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5779,7 +5774,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259766</v>
+        <v>121259767</v>
       </c>
       <c r="B45" t="n">
         <v>98081</v>
@@ -5814,7 +5809,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5841,7 +5836,7 @@
         <v>551637</v>
       </c>
       <c r="R45" t="n">
-        <v>6636229</v>
+        <v>6636228</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5900,10 +5895,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121259709</v>
+        <v>121259710</v>
       </c>
       <c r="B46" t="n">
-        <v>91137</v>
+        <v>90697</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5912,25 +5907,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6025,10 +6020,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121259710</v>
+        <v>121259764</v>
       </c>
       <c r="B47" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6037,43 +6032,57 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551258</v>
+        <v>551417</v>
       </c>
       <c r="R47" t="n">
-        <v>6636221</v>
+        <v>6636227</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6116,24 +6125,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6150,10 +6141,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121259764</v>
+        <v>121259711</v>
       </c>
       <c r="B48" t="n">
-        <v>98081</v>
+        <v>90662</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6162,57 +6153,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551417</v>
+        <v>551324</v>
       </c>
       <c r="R48" t="n">
-        <v>6636227</v>
+        <v>6636145</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6247,6 +6224,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Barklös granlåga</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6255,6 +6237,24 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5141,10 +5141,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121259712</v>
+        <v>121259766</v>
       </c>
       <c r="B40" t="n">
-        <v>91137</v>
+        <v>98094</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5157,27 +5157,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5232,14 +5246,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5256,10 +5262,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259797</v>
+        <v>121259710</v>
       </c>
       <c r="B41" t="n">
-        <v>43707</v>
+        <v>90709</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5268,50 +5274,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101735</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>kokong</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5320,10 +5307,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551271</v>
+        <v>551258</v>
       </c>
       <c r="R41" t="n">
-        <v>6636238</v>
+        <v>6636221</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5358,11 +5345,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5374,17 +5356,20 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
-        </is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN41" t="n">
+        <v>1</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5402,10 +5387,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259709</v>
+        <v>121259767</v>
       </c>
       <c r="B42" t="n">
-        <v>91137</v>
+        <v>98094</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5418,39 +5403,53 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551258</v>
+        <v>551637</v>
       </c>
       <c r="R42" t="n">
-        <v>6636221</v>
+        <v>6636228</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5493,24 +5492,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5527,10 +5508,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259765</v>
+        <v>121259797</v>
       </c>
       <c r="B43" t="n">
-        <v>98081</v>
+        <v>43707</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5539,40 +5520,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>kokong</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5582,14 +5568,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551423</v>
+        <v>551271</v>
       </c>
       <c r="R43" t="n">
-        <v>6636218</v>
+        <v>6636238</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5626,7 +5612,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5637,6 +5623,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5653,10 +5654,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259766</v>
+        <v>121259711</v>
       </c>
       <c r="B44" t="n">
-        <v>98081</v>
+        <v>90674</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5665,57 +5666,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551637</v>
+        <v>551324</v>
       </c>
       <c r="R44" t="n">
-        <v>6636229</v>
+        <v>6636145</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5750,6 +5737,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Barklös granlåga</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5758,6 +5750,24 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5774,10 +5784,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259767</v>
+        <v>121259712</v>
       </c>
       <c r="B45" t="n">
-        <v>98081</v>
+        <v>91149</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5790,41 +5800,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5836,7 +5832,7 @@
         <v>551637</v>
       </c>
       <c r="R45" t="n">
-        <v>6636228</v>
+        <v>6636229</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5879,6 +5875,14 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5895,10 +5899,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121259710</v>
+        <v>121259765</v>
       </c>
       <c r="B46" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5907,43 +5911,57 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551258</v>
+        <v>551423</v>
       </c>
       <c r="R46" t="n">
-        <v>6636221</v>
+        <v>6636218</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5978,6 +5996,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5986,24 +6009,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6023,7 +6028,7 @@
         <v>121259764</v>
       </c>
       <c r="B47" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6141,10 +6146,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121259711</v>
+        <v>121259709</v>
       </c>
       <c r="B48" t="n">
-        <v>90662</v>
+        <v>91149</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6153,25 +6158,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6186,10 +6191,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551324</v>
+        <v>551258</v>
       </c>
       <c r="R48" t="n">
-        <v>6636145</v>
+        <v>6636221</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6222,11 +6227,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Barklös granlåga</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5141,10 +5141,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121259766</v>
+        <v>121259767</v>
       </c>
       <c r="B40" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5203,7 +5203,7 @@
         <v>551637</v>
       </c>
       <c r="R40" t="n">
-        <v>6636229</v>
+        <v>6636228</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5262,10 +5262,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259710</v>
+        <v>121259764</v>
       </c>
       <c r="B41" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5274,43 +5274,57 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551258</v>
+        <v>551417</v>
       </c>
       <c r="R41" t="n">
-        <v>6636221</v>
+        <v>6636227</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5353,24 +5367,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5387,10 +5383,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259767</v>
+        <v>121259709</v>
       </c>
       <c r="B42" t="n">
-        <v>98094</v>
+        <v>91150</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5403,53 +5399,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551637</v>
+        <v>551258</v>
       </c>
       <c r="R42" t="n">
-        <v>6636228</v>
+        <v>6636221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5492,6 +5474,24 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5508,10 +5508,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259797</v>
+        <v>121259712</v>
       </c>
       <c r="B43" t="n">
-        <v>43707</v>
+        <v>91150</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5520,62 +5520,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101735</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>kokong</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551271</v>
+        <v>551637</v>
       </c>
       <c r="R43" t="n">
-        <v>6636238</v>
+        <v>6636229</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5610,11 +5591,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5624,19 +5600,12 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
+      <c r="AN43" t="n">
+        <v>1</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5654,10 +5623,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259711</v>
+        <v>121259766</v>
       </c>
       <c r="B44" t="n">
-        <v>90674</v>
+        <v>98095</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5666,43 +5635,57 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551324</v>
+        <v>551637</v>
       </c>
       <c r="R44" t="n">
-        <v>6636145</v>
+        <v>6636229</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5737,11 +5720,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Barklös granlåga</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5750,24 +5728,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5784,10 +5744,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259712</v>
+        <v>121259797</v>
       </c>
       <c r="B45" t="n">
-        <v>91149</v>
+        <v>43707</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5796,43 +5756,62 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>101735</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>kokong</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551637</v>
+        <v>551271</v>
       </c>
       <c r="R45" t="n">
-        <v>6636229</v>
+        <v>6636238</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5867,6 +5846,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5876,12 +5860,19 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AN45" t="n">
-        <v>1</v>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5899,10 +5890,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121259765</v>
+        <v>121259711</v>
       </c>
       <c r="B46" t="n">
-        <v>98094</v>
+        <v>90675</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5911,57 +5902,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551423</v>
+        <v>551324</v>
       </c>
       <c r="R46" t="n">
-        <v>6636218</v>
+        <v>6636145</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5998,7 +5975,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
+          <t>Barklös granlåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6009,6 +5986,24 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6025,10 +6020,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121259764</v>
+        <v>121259710</v>
       </c>
       <c r="B47" t="n">
-        <v>98094</v>
+        <v>90710</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6037,57 +6032,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551417</v>
+        <v>551258</v>
       </c>
       <c r="R47" t="n">
-        <v>6636227</v>
+        <v>6636221</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6130,6 +6111,24 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6146,10 +6145,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121259709</v>
+        <v>121259765</v>
       </c>
       <c r="B48" t="n">
-        <v>91149</v>
+        <v>98095</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6162,39 +6161,53 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551258</v>
+        <v>551423</v>
       </c>
       <c r="R48" t="n">
-        <v>6636221</v>
+        <v>6636218</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6229,6 +6242,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6237,24 +6255,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5141,10 +5141,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121259767</v>
+        <v>121259712</v>
       </c>
       <c r="B40" t="n">
-        <v>98095</v>
+        <v>91153</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5157,41 +5157,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5203,7 +5189,7 @@
         <v>551637</v>
       </c>
       <c r="R40" t="n">
-        <v>6636228</v>
+        <v>6636229</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5246,6 +5232,14 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5262,10 +5256,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259764</v>
+        <v>121259767</v>
       </c>
       <c r="B41" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5317,14 +5311,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551417</v>
+        <v>551637</v>
       </c>
       <c r="R41" t="n">
-        <v>6636227</v>
+        <v>6636228</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5383,10 +5377,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259709</v>
+        <v>121259797</v>
       </c>
       <c r="B42" t="n">
-        <v>91150</v>
+        <v>43710</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5395,31 +5389,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>101735</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>kokong</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5428,10 +5441,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551258</v>
+        <v>551271</v>
       </c>
       <c r="R42" t="n">
-        <v>6636221</v>
+        <v>6636238</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5466,6 +5479,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5477,20 +5495,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN42" t="n">
-        <v>1</v>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5508,10 +5523,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259712</v>
+        <v>121259766</v>
       </c>
       <c r="B43" t="n">
-        <v>91150</v>
+        <v>98098</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5524,27 +5539,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5599,14 +5628,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5623,10 +5644,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259766</v>
+        <v>121259764</v>
       </c>
       <c r="B44" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5658,7 +5679,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5678,14 +5699,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551637</v>
+        <v>551417</v>
       </c>
       <c r="R44" t="n">
-        <v>6636229</v>
+        <v>6636227</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5744,10 +5765,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259797</v>
+        <v>121259711</v>
       </c>
       <c r="B45" t="n">
-        <v>43707</v>
+        <v>90678</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5760,46 +5781,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>kokong</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5808,10 +5810,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551271</v>
+        <v>551324</v>
       </c>
       <c r="R45" t="n">
-        <v>6636238</v>
+        <v>6636145</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5848,7 +5850,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
+          <t>Barklös granlåga</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5862,17 +5864,20 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
-        </is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>1</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5890,10 +5895,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121259711</v>
+        <v>121259710</v>
       </c>
       <c r="B46" t="n">
-        <v>90675</v>
+        <v>90713</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5902,25 +5907,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5935,10 +5940,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551324</v>
+        <v>551258</v>
       </c>
       <c r="R46" t="n">
-        <v>6636145</v>
+        <v>6636221</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5971,11 +5976,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Barklös granlåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6020,10 +6020,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121259710</v>
+        <v>121259709</v>
       </c>
       <c r="B47" t="n">
-        <v>90710</v>
+        <v>91153</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6032,25 +6032,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6148,7 +6148,7 @@
         <v>121259765</v>
       </c>
       <c r="B48" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5141,10 +5141,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121259712</v>
+        <v>121259767</v>
       </c>
       <c r="B40" t="n">
-        <v>91153</v>
+        <v>98098</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5157,27 +5157,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5189,7 +5203,7 @@
         <v>551637</v>
       </c>
       <c r="R40" t="n">
-        <v>6636229</v>
+        <v>6636228</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5232,14 +5246,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5256,7 +5262,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259767</v>
+        <v>121259766</v>
       </c>
       <c r="B41" t="n">
         <v>98098</v>
@@ -5291,7 +5297,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5318,7 +5324,7 @@
         <v>551637</v>
       </c>
       <c r="R41" t="n">
-        <v>6636228</v>
+        <v>6636229</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5377,10 +5383,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259797</v>
+        <v>121259709</v>
       </c>
       <c r="B42" t="n">
-        <v>43710</v>
+        <v>91153</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5389,50 +5395,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101735</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>kokong</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5441,10 +5428,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551271</v>
+        <v>551258</v>
       </c>
       <c r="R42" t="n">
-        <v>6636238</v>
+        <v>6636221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5479,11 +5466,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5495,17 +5477,20 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
-        </is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN42" t="n">
+        <v>1</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5523,7 +5508,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259766</v>
+        <v>121259765</v>
       </c>
       <c r="B43" t="n">
         <v>98098</v>
@@ -5558,17 +5543,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5578,14 +5563,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551637</v>
+        <v>551423</v>
       </c>
       <c r="R43" t="n">
-        <v>6636229</v>
+        <v>6636218</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5618,6 +5603,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5644,10 +5634,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259764</v>
+        <v>121259797</v>
       </c>
       <c r="B44" t="n">
-        <v>98098</v>
+        <v>43710</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5656,40 +5646,45 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>kokong</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5699,14 +5694,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551417</v>
+        <v>551271</v>
       </c>
       <c r="R44" t="n">
-        <v>6636227</v>
+        <v>6636238</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5741,6 +5736,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5749,6 +5749,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5765,10 +5780,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259711</v>
+        <v>121259764</v>
       </c>
       <c r="B45" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5777,43 +5792,57 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551324</v>
+        <v>551417</v>
       </c>
       <c r="R45" t="n">
-        <v>6636145</v>
+        <v>6636227</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5848,11 +5877,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Barklös granlåga</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5861,24 +5885,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6020,10 +6026,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121259709</v>
+        <v>121259711</v>
       </c>
       <c r="B47" t="n">
-        <v>91153</v>
+        <v>90678</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6032,25 +6038,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6065,10 +6071,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551258</v>
+        <v>551324</v>
       </c>
       <c r="R47" t="n">
-        <v>6636221</v>
+        <v>6636145</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6101,6 +6107,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Barklös granlåga</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6145,10 +6156,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121259765</v>
+        <v>121259712</v>
       </c>
       <c r="B48" t="n">
-        <v>98098</v>
+        <v>91153</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6161,53 +6172,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551423</v>
+        <v>551637</v>
       </c>
       <c r="R48" t="n">
-        <v>6636218</v>
+        <v>6636229</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6242,11 +6239,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6255,6 +6247,14 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5508,10 +5508,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259765</v>
+        <v>121259797</v>
       </c>
       <c r="B43" t="n">
-        <v>98098</v>
+        <v>43710</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5520,40 +5520,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>kokong</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5563,14 +5568,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551423</v>
+        <v>551271</v>
       </c>
       <c r="R43" t="n">
-        <v>6636218</v>
+        <v>6636238</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5607,7 +5612,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5618,6 +5623,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5634,10 +5654,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259797</v>
+        <v>121259765</v>
       </c>
       <c r="B44" t="n">
-        <v>43710</v>
+        <v>98098</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5646,45 +5666,40 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>kokong</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5694,14 +5709,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551271</v>
+        <v>551423</v>
       </c>
       <c r="R44" t="n">
-        <v>6636238</v>
+        <v>6636218</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5738,7 +5753,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5749,21 +5764,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5141,10 +5141,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121259767</v>
+        <v>121259709</v>
       </c>
       <c r="B40" t="n">
-        <v>98098</v>
+        <v>91159</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5157,53 +5157,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>551637</v>
+        <v>551258</v>
       </c>
       <c r="R40" t="n">
-        <v>6636228</v>
+        <v>6636221</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5246,6 +5232,24 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5265,7 +5269,7 @@
         <v>121259766</v>
       </c>
       <c r="B41" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5383,10 +5387,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259709</v>
+        <v>121259764</v>
       </c>
       <c r="B42" t="n">
-        <v>91153</v>
+        <v>98104</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5399,39 +5403,53 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551258</v>
+        <v>551417</v>
       </c>
       <c r="R42" t="n">
-        <v>6636221</v>
+        <v>6636227</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5474,24 +5492,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5508,10 +5508,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259797</v>
+        <v>121259711</v>
       </c>
       <c r="B43" t="n">
-        <v>43710</v>
+        <v>90684</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5524,46 +5524,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>kokong</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5572,10 +5553,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551271</v>
+        <v>551324</v>
       </c>
       <c r="R43" t="n">
-        <v>6636238</v>
+        <v>6636145</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5612,7 +5593,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
+          <t>Barklös granlåga</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5626,17 +5607,20 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
-        </is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN43" t="n">
+        <v>1</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5654,10 +5638,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259765</v>
+        <v>121259767</v>
       </c>
       <c r="B44" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5694,12 +5678,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5709,14 +5693,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551423</v>
+        <v>551637</v>
       </c>
       <c r="R44" t="n">
-        <v>6636218</v>
+        <v>6636228</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5749,11 +5733,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5780,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259764</v>
+        <v>121259712</v>
       </c>
       <c r="B45" t="n">
-        <v>98098</v>
+        <v>91159</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5796,53 +5775,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551417</v>
+        <v>551637</v>
       </c>
       <c r="R45" t="n">
-        <v>6636227</v>
+        <v>6636229</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5885,6 +5850,14 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5901,10 +5874,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121259710</v>
+        <v>121259797</v>
       </c>
       <c r="B46" t="n">
-        <v>90713</v>
+        <v>43711</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5913,31 +5886,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>101735</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>kokong</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5946,10 +5938,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551258</v>
+        <v>551271</v>
       </c>
       <c r="R46" t="n">
-        <v>6636221</v>
+        <v>6636238</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5984,6 +5976,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5995,20 +5992,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN46" t="n">
-        <v>1</v>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6026,10 +6020,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121259711</v>
+        <v>121259765</v>
       </c>
       <c r="B47" t="n">
-        <v>90678</v>
+        <v>98104</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6038,43 +6032,57 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551324</v>
+        <v>551423</v>
       </c>
       <c r="R47" t="n">
-        <v>6636145</v>
+        <v>6636218</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6111,7 +6119,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Barklös granlåga</t>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6122,24 +6130,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6156,10 +6146,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121259712</v>
+        <v>121259710</v>
       </c>
       <c r="B48" t="n">
-        <v>91153</v>
+        <v>90719</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6168,25 +6158,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6197,14 +6187,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551637</v>
+        <v>551258</v>
       </c>
       <c r="R48" t="n">
-        <v>6636229</v>
+        <v>6636221</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6248,12 +6238,22 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AN48" t="n">
         <v>1</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5759,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259712</v>
+        <v>121259765</v>
       </c>
       <c r="B45" t="n">
-        <v>91159</v>
+        <v>98104</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5775,39 +5775,53 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551637</v>
+        <v>551423</v>
       </c>
       <c r="R45" t="n">
-        <v>6636229</v>
+        <v>6636218</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5842,6 +5856,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5850,14 +5869,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5874,10 +5885,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121259797</v>
+        <v>121259712</v>
       </c>
       <c r="B46" t="n">
-        <v>43711</v>
+        <v>91159</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5886,62 +5897,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101735</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>kokong</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551271</v>
+        <v>551637</v>
       </c>
       <c r="R46" t="n">
-        <v>6636238</v>
+        <v>6636229</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5976,11 +5968,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5990,19 +5977,12 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
+      <c r="AN46" t="n">
+        <v>1</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6020,10 +6000,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121259765</v>
+        <v>121259797</v>
       </c>
       <c r="B47" t="n">
-        <v>98104</v>
+        <v>43711</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6032,40 +6012,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>kokong</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6075,14 +6060,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551423</v>
+        <v>551271</v>
       </c>
       <c r="R47" t="n">
-        <v>6636218</v>
+        <v>6636238</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6119,7 +6104,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6130,6 +6115,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5141,10 +5141,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121259709</v>
+        <v>121259766</v>
       </c>
       <c r="B40" t="n">
-        <v>91159</v>
+        <v>98105</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5157,39 +5157,53 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>551258</v>
+        <v>551637</v>
       </c>
       <c r="R40" t="n">
-        <v>6636221</v>
+        <v>6636229</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5232,24 +5246,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5266,10 +5262,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259766</v>
+        <v>121259711</v>
       </c>
       <c r="B41" t="n">
-        <v>98104</v>
+        <v>90685</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5278,57 +5274,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551637</v>
+        <v>551324</v>
       </c>
       <c r="R41" t="n">
-        <v>6636229</v>
+        <v>6636145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5363,6 +5345,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Barklös granlåga</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5371,6 +5358,24 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5387,10 +5392,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259764</v>
+        <v>121259767</v>
       </c>
       <c r="B42" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5442,14 +5447,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551417</v>
+        <v>551637</v>
       </c>
       <c r="R42" t="n">
-        <v>6636227</v>
+        <v>6636228</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5508,10 +5513,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259711</v>
+        <v>121259765</v>
       </c>
       <c r="B43" t="n">
-        <v>90684</v>
+        <v>98105</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5520,43 +5525,57 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551324</v>
+        <v>551423</v>
       </c>
       <c r="R43" t="n">
-        <v>6636145</v>
+        <v>6636218</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5593,7 +5612,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Barklös granlåga</t>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5604,24 +5623,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5638,10 +5639,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259767</v>
+        <v>121259709</v>
       </c>
       <c r="B44" t="n">
-        <v>98104</v>
+        <v>91160</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5654,53 +5655,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551637</v>
+        <v>551258</v>
       </c>
       <c r="R44" t="n">
-        <v>6636228</v>
+        <v>6636221</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5743,6 +5730,24 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5759,10 +5764,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259765</v>
+        <v>121259764</v>
       </c>
       <c r="B45" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5799,12 +5804,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5818,10 +5823,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551423</v>
+        <v>551417</v>
       </c>
       <c r="R45" t="n">
-        <v>6636218</v>
+        <v>6636227</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5854,11 +5859,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5885,10 +5885,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121259712</v>
+        <v>121259710</v>
       </c>
       <c r="B46" t="n">
-        <v>91159</v>
+        <v>90720</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5897,25 +5897,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5926,14 +5926,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551637</v>
+        <v>551258</v>
       </c>
       <c r="R46" t="n">
-        <v>6636229</v>
+        <v>6636221</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5977,12 +5977,22 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AN46" t="n">
         <v>1</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6000,10 +6010,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121259797</v>
+        <v>121259712</v>
       </c>
       <c r="B47" t="n">
-        <v>43711</v>
+        <v>91160</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6012,62 +6022,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101735</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>kokong</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551271</v>
+        <v>551637</v>
       </c>
       <c r="R47" t="n">
-        <v>6636238</v>
+        <v>6636229</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6102,11 +6093,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6116,19 +6102,12 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
+      <c r="AN47" t="n">
+        <v>1</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6146,10 +6125,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121259710</v>
+        <v>121259797</v>
       </c>
       <c r="B48" t="n">
-        <v>90719</v>
+        <v>43711</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6158,31 +6137,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>101735</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>kokong</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6191,10 +6189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551258</v>
+        <v>551271</v>
       </c>
       <c r="R48" t="n">
-        <v>6636221</v>
+        <v>6636238</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6229,6 +6227,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6240,20 +6243,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN48" t="n">
-        <v>1</v>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5141,7 +5141,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121259766</v>
+        <v>121259767</v>
       </c>
       <c r="B40" t="n">
         <v>98105</v>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5203,7 +5203,7 @@
         <v>551637</v>
       </c>
       <c r="R40" t="n">
-        <v>6636229</v>
+        <v>6636228</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5262,10 +5262,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259711</v>
+        <v>121259764</v>
       </c>
       <c r="B41" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5274,43 +5274,57 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551324</v>
+        <v>551417</v>
       </c>
       <c r="R41" t="n">
-        <v>6636145</v>
+        <v>6636227</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5345,11 +5359,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Barklös granlåga</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5358,24 +5367,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5392,7 +5383,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259767</v>
+        <v>121259765</v>
       </c>
       <c r="B42" t="n">
         <v>98105</v>
@@ -5432,12 +5423,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5447,14 +5438,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551637</v>
+        <v>551423</v>
       </c>
       <c r="R42" t="n">
-        <v>6636228</v>
+        <v>6636218</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5487,6 +5478,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5513,10 +5509,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259765</v>
+        <v>121259710</v>
       </c>
       <c r="B43" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5525,57 +5521,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551423</v>
+        <v>551258</v>
       </c>
       <c r="R43" t="n">
-        <v>6636218</v>
+        <v>6636221</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5610,11 +5592,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5623,6 +5600,24 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5639,10 +5634,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259709</v>
+        <v>121259766</v>
       </c>
       <c r="B44" t="n">
-        <v>91160</v>
+        <v>98105</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5655,39 +5650,53 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551258</v>
+        <v>551637</v>
       </c>
       <c r="R44" t="n">
-        <v>6636221</v>
+        <v>6636229</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5730,24 +5739,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5764,10 +5755,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259764</v>
+        <v>121259711</v>
       </c>
       <c r="B45" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5776,57 +5767,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551417</v>
+        <v>551324</v>
       </c>
       <c r="R45" t="n">
-        <v>6636227</v>
+        <v>6636145</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,6 +5838,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Barklös granlåga</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5869,6 +5851,24 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5885,10 +5885,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121259710</v>
+        <v>121259709</v>
       </c>
       <c r="B46" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5897,25 +5897,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121259712</v>
+        <v>121259797</v>
       </c>
       <c r="B47" t="n">
-        <v>91160</v>
+        <v>43711</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6022,43 +6022,62 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>101735</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>kokong</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551637</v>
+        <v>551271</v>
       </c>
       <c r="R47" t="n">
-        <v>6636229</v>
+        <v>6636238</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6093,6 +6112,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6102,12 +6126,19 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AN47" t="n">
-        <v>1</v>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6125,10 +6156,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121259797</v>
+        <v>121259712</v>
       </c>
       <c r="B48" t="n">
-        <v>43711</v>
+        <v>91160</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6137,62 +6168,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>101735</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>kokong</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551271</v>
+        <v>551637</v>
       </c>
       <c r="R48" t="n">
-        <v>6636238</v>
+        <v>6636229</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6227,11 +6239,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6241,19 +6248,12 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
+      <c r="AN48" t="n">
+        <v>1</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5141,10 +5141,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121259767</v>
+        <v>121259711</v>
       </c>
       <c r="B40" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5153,57 +5153,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>551637</v>
+        <v>551324</v>
       </c>
       <c r="R40" t="n">
-        <v>6636228</v>
+        <v>6636145</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5238,6 +5224,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Barklös granlåga</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5246,6 +5237,24 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5262,10 +5271,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259764</v>
+        <v>121259712</v>
       </c>
       <c r="B41" t="n">
-        <v>98105</v>
+        <v>91160</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5278,53 +5287,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551417</v>
+        <v>551637</v>
       </c>
       <c r="R41" t="n">
-        <v>6636227</v>
+        <v>6636229</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5367,6 +5362,14 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5383,10 +5386,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259765</v>
+        <v>121259710</v>
       </c>
       <c r="B42" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5395,57 +5398,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551423</v>
+        <v>551258</v>
       </c>
       <c r="R42" t="n">
-        <v>6636218</v>
+        <v>6636221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5480,11 +5469,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5493,6 +5477,24 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5509,10 +5511,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259710</v>
+        <v>121259709</v>
       </c>
       <c r="B43" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5521,25 +5523,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5634,7 +5636,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259766</v>
+        <v>121259765</v>
       </c>
       <c r="B44" t="n">
         <v>98105</v>
@@ -5669,17 +5671,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5689,14 +5691,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551637</v>
+        <v>551423</v>
       </c>
       <c r="R44" t="n">
-        <v>6636229</v>
+        <v>6636218</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5729,6 +5731,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5755,10 +5762,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259711</v>
+        <v>121259797</v>
       </c>
       <c r="B45" t="n">
-        <v>90685</v>
+        <v>43711</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5771,27 +5778,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>101735</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>kokong</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5800,10 +5826,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551324</v>
+        <v>551271</v>
       </c>
       <c r="R45" t="n">
-        <v>6636145</v>
+        <v>6636238</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5840,7 +5866,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Barklös granlåga</t>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5854,20 +5880,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN45" t="n">
-        <v>1</v>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5885,10 +5908,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121259709</v>
+        <v>121259764</v>
       </c>
       <c r="B46" t="n">
-        <v>91160</v>
+        <v>98105</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5901,39 +5924,53 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551258</v>
+        <v>551417</v>
       </c>
       <c r="R46" t="n">
-        <v>6636221</v>
+        <v>6636227</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5976,24 +6013,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6010,10 +6029,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121259797</v>
+        <v>121259767</v>
       </c>
       <c r="B47" t="n">
-        <v>43711</v>
+        <v>98105</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6022,45 +6041,40 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>kokong</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6070,14 +6084,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551271</v>
+        <v>551637</v>
       </c>
       <c r="R47" t="n">
-        <v>6636238</v>
+        <v>6636228</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6112,11 +6126,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6125,21 +6134,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6156,10 +6150,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121259712</v>
+        <v>121259766</v>
       </c>
       <c r="B48" t="n">
-        <v>91160</v>
+        <v>98105</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6172,27 +6166,41 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6247,14 +6255,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -5141,10 +5141,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121259711</v>
+        <v>121259764</v>
       </c>
       <c r="B40" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5153,43 +5153,57 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>551324</v>
+        <v>551417</v>
       </c>
       <c r="R40" t="n">
-        <v>6636145</v>
+        <v>6636227</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5224,11 +5238,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Barklös granlåga</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5237,24 +5246,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5271,10 +5262,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259712</v>
+        <v>121259766</v>
       </c>
       <c r="B41" t="n">
-        <v>91160</v>
+        <v>98105</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5287,27 +5278,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5362,14 +5367,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5386,10 +5383,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259710</v>
+        <v>121259767</v>
       </c>
       <c r="B42" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5398,43 +5395,57 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551258</v>
+        <v>551637</v>
       </c>
       <c r="R42" t="n">
-        <v>6636221</v>
+        <v>6636228</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5477,24 +5488,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5636,10 +5629,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259765</v>
+        <v>121259711</v>
       </c>
       <c r="B44" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5648,57 +5641,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551423</v>
+        <v>551324</v>
       </c>
       <c r="R44" t="n">
-        <v>6636218</v>
+        <v>6636145</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5735,7 +5714,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
+          <t>Barklös granlåga</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5746,6 +5725,24 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5762,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259797</v>
+        <v>121259765</v>
       </c>
       <c r="B45" t="n">
-        <v>43711</v>
+        <v>98105</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5774,45 +5771,40 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>kokong</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5822,14 +5814,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551271</v>
+        <v>551423</v>
       </c>
       <c r="R45" t="n">
-        <v>6636238</v>
+        <v>6636218</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5866,7 +5858,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5877,21 +5869,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5908,10 +5885,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121259764</v>
+        <v>121259712</v>
       </c>
       <c r="B46" t="n">
-        <v>98105</v>
+        <v>91160</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5924,53 +5901,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551417</v>
+        <v>551637</v>
       </c>
       <c r="R46" t="n">
-        <v>6636227</v>
+        <v>6636229</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6013,6 +5976,14 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6029,10 +6000,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121259767</v>
+        <v>121259797</v>
       </c>
       <c r="B47" t="n">
-        <v>98105</v>
+        <v>43711</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6041,40 +6012,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>kokong</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6084,14 +6060,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551637</v>
+        <v>551271</v>
       </c>
       <c r="R47" t="n">
-        <v>6636228</v>
+        <v>6636238</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6126,6 +6102,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6134,6 +6115,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6150,10 +6146,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121259766</v>
+        <v>121259710</v>
       </c>
       <c r="B48" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6162,57 +6158,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551637</v>
+        <v>551258</v>
       </c>
       <c r="R48" t="n">
-        <v>6636229</v>
+        <v>6636221</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6255,6 +6237,24 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 10792-2020 artfynd.xlsx
+++ b/artfynd/A 10792-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4126,7 +4126,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>65332017</v>
+        <v>65332018</v>
       </c>
       <c r="B32" t="n">
         <v>96334</v>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>551035.7915213298</v>
+        <v>551333.1979371613</v>
       </c>
       <c r="R32" t="n">
-        <v>6636463.118776147</v>
+        <v>6636680.210346036</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>65332018</v>
+        <v>86992148</v>
       </c>
       <c r="B33" t="n">
         <v>96334</v>
@@ -4271,20 +4271,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långviken, Vstm</t>
+          <t>Långviken, Trummelsberg, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>551333.1979371613</v>
+        <v>551306.1291460483</v>
       </c>
       <c r="R33" t="n">
-        <v>6636680.210346036</v>
+        <v>6636672.803455198</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4308,7 +4322,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2014-05-01</t>
+          <t>2020-01-27</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4318,7 +4332,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2020-01-27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4334,23 +4348,28 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Jacob Rudhe, Mårten Berglind</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>88354331</v>
+        <v>88616827</v>
       </c>
       <c r="B34" t="n">
         <v>96334</v>
@@ -4383,20 +4402,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långviken 4, Ö om Torvmossen (knärot), Vstm</t>
+          <t>Långviken, 100 m V Jonssons mosse (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>551333.7079607621</v>
+        <v>551446.9769484408</v>
       </c>
       <c r="R34" t="n">
-        <v>6636679.715085428</v>
+        <v>6636385.407075317</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4420,12 +4453,12 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>U-Fag-0267</t>
+          <t>U-Fag-0271</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2014-05-01</t>
+          <t>2020-01-27</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4435,7 +4468,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2020-01-27</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4451,6 +4484,11 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4460,7 +4498,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Jacob Rudhe, Mårten Berglind</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4471,67 +4509,60 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>86992148</v>
+        <v>106485943</v>
       </c>
       <c r="B35" t="n">
-        <v>96334</v>
+        <v>89392</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långviken, Trummelsberg, Vstm</t>
+          <t>Långvikens naturreservat, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>551306.1291460483</v>
+        <v>551246.2292929499</v>
       </c>
       <c r="R35" t="n">
-        <v>6636672.803455198</v>
+        <v>6636127.925128792</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4555,7 +4586,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2020-01-27</t>
+          <t>2023-02-03</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4565,7 +4596,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2020-01-27</t>
+          <t>2023-02-03</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4579,70 +4610,85 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Mårten Berglind</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>88616827</v>
+        <v>106485953</v>
       </c>
       <c r="B36" t="n">
-        <v>96334</v>
+        <v>95519</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4650,19 +4696,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långviken, 100 m V Jonssons mosse (knärot), Vstm</t>
+          <t>Långvikens naturreservat, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>551446.9769484408</v>
+        <v>551568.3053368289</v>
       </c>
       <c r="R36" t="n">
-        <v>6636385.407075317</v>
+        <v>6636453.90439632</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4684,14 +4732,9 @@
           <t>Västervåla</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>U-Fag-0271</t>
-        </is>
-      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2020-01-27</t>
+          <t>2023-02-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4701,7 +4744,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2020-01-27</t>
+          <t>2023-02-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -4715,41 +4758,33 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Mårten Berglind</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>86992149</v>
+        <v>121259764</v>
       </c>
       <c r="B37" t="n">
-        <v>96334</v>
+        <v>98105</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4777,29 +4812,34 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långviken, Trummelsberg, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>551446.9839126548</v>
+        <v>551417</v>
       </c>
       <c r="R37" t="n">
-        <v>6636384.904814027</v>
+        <v>6636227</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4826,22 +4866,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2020-01-27</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2020-01-27</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4852,31 +4882,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Mårten Berglind</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>106485943</v>
+        <v>121259766</v>
       </c>
       <c r="B38" t="n">
-        <v>89392</v>
+        <v>98105</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4885,48 +4910,60 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långvikens naturreservat, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>551246.2292929499</v>
+        <v>551637</v>
       </c>
       <c r="R38" t="n">
-        <v>6636127.925128792</v>
+        <v>6636229</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4950,22 +4987,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-02-03</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-02-03</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4974,32 +5001,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AN38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5016,10 +5019,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>106485953</v>
+        <v>121259767</v>
       </c>
       <c r="B39" t="n">
-        <v>95519</v>
+        <v>98105</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5028,53 +5031,60 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långvikens naturreservat, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>551568.3053368289</v>
+        <v>551637</v>
       </c>
       <c r="R39" t="n">
-        <v>6636453.90439632</v>
+        <v>6636228</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5098,22 +5108,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-02-03</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-02-03</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5122,7 +5122,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5141,10 +5140,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121259764</v>
+        <v>121259709</v>
       </c>
       <c r="B40" t="n">
-        <v>98105</v>
+        <v>91160</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5157,53 +5156,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>551417</v>
+        <v>551258</v>
       </c>
       <c r="R40" t="n">
-        <v>6636227</v>
+        <v>6636221</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5246,6 +5231,24 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5262,10 +5265,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121259766</v>
+        <v>121259711</v>
       </c>
       <c r="B41" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5274,57 +5277,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551637</v>
+        <v>551324</v>
       </c>
       <c r="R41" t="n">
-        <v>6636229</v>
+        <v>6636145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5359,6 +5348,11 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Barklös granlåga</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5367,6 +5361,24 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5383,7 +5395,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121259767</v>
+        <v>121259765</v>
       </c>
       <c r="B42" t="n">
         <v>98105</v>
@@ -5423,12 +5435,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5438,14 +5450,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551637</v>
+        <v>551423</v>
       </c>
       <c r="R42" t="n">
-        <v>6636228</v>
+        <v>6636218</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5478,6 +5490,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ca 2m2, 19 stjälkar räknade</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5504,7 +5521,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121259709</v>
+        <v>121259712</v>
       </c>
       <c r="B43" t="n">
         <v>91160</v>
@@ -5545,14 +5562,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
+          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551258</v>
+        <v>551637</v>
       </c>
       <c r="R43" t="n">
-        <v>6636221</v>
+        <v>6636229</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5596,22 +5613,12 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AN43" t="n">
         <v>1</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5629,10 +5636,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121259711</v>
+        <v>121259797</v>
       </c>
       <c r="B44" t="n">
-        <v>90685</v>
+        <v>43711</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5645,27 +5652,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>101735</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>puppa</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>kokong</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5674,10 +5700,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551324</v>
+        <v>551271</v>
       </c>
       <c r="R44" t="n">
-        <v>6636145</v>
+        <v>6636238</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5714,7 +5740,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Barklös granlåga</t>
+          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5728,20 +5754,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN44" t="n">
-        <v>1</v>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5759,10 +5782,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121259765</v>
+        <v>121259710</v>
       </c>
       <c r="B45" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5771,57 +5794,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Jonssons mosse (SV om), Långvikens NR, Vstm</t>
+          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>551423</v>
+        <v>551258</v>
       </c>
       <c r="R45" t="n">
-        <v>6636218</v>
+        <v>6636221</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5856,11 +5865,6 @@
           <t>2024-10-14</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ca 2m2, 19 stjälkar räknade</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5869,6 +5873,24 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5882,392 +5904,6 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>121259712</v>
-      </c>
-      <c r="B46" t="n">
-        <v>91160</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Jonssons mosse (S om), Långvikens NR, Vstm</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>551637</v>
-      </c>
-      <c r="R46" t="n">
-        <v>6636229</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Fagersta</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Västervåla</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Markus Rehnberg</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Markus Rehnberg</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>121259797</v>
-      </c>
-      <c r="B47" t="n">
-        <v>43711</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>101735</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Jättesvampmal</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Scardia boletella</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>kokong</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>551271</v>
-      </c>
-      <c r="R47" t="n">
-        <v>6636238</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Fagersta</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Västervåla</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Fyra intakta larvhudar utsprugna ur fnöskticka på björkhögstubbe</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Markus Rehnberg</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Markus Rehnberg</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>121259710</v>
-      </c>
-      <c r="B48" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Torvmossen (S om), Långvikens NR, Vstm</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>551258</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6636221</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Fagersta</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Västervåla</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2024-10-14</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Liggande trädstam # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Markus Rehnberg</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Markus Rehnberg</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
